--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1254,7 +1254,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2541,10 +2541,10 @@
         <v>0.606214</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J80" t="n">
         <v>1</v>
@@ -9123,7 +9123,7 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -9292,10 +9292,10 @@
         <v>0.874973</v>
       </c>
       <c r="H206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>1</v>
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -10069,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
         <v>0</v>
       </c>
       <c r="I225" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -10284,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -10327,7 +10327,7 @@
         <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -10370,7 +10370,7 @@
         <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J231" t="n">
         <v>1</v>
@@ -10413,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -10542,7 +10542,7 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J235" t="n">
         <v>1</v>
@@ -10585,7 +10585,7 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -10843,7 +10843,7 @@
         <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -10926,10 +10926,10 @@
         <v>0.796082</v>
       </c>
       <c r="H244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I244" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -11012,10 +11012,10 @@
         <v>0.799498</v>
       </c>
       <c r="H246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J246" t="n">
         <v>1</v>
@@ -11187,7 +11187,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J250" t="n">
         <v>1</v>
@@ -11273,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J252" t="n">
         <v>1</v>
@@ -11445,7 +11445,7 @@
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J256" t="n">
         <v>1</v>
@@ -11488,7 +11488,7 @@
         <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>0.333333</v>
+        <v>0.4</v>
       </c>
       <c r="J257" t="n">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>0</v>
       </c>
       <c r="I258" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J258" t="n">
         <v>1</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J259" t="n">
         <v>1</v>
@@ -11703,7 +11703,7 @@
         <v>0</v>
       </c>
       <c r="I262" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -11786,10 +11786,10 @@
         <v>0.990796</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0.666667</v>
+        <v>0.4</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
@@ -11961,7 +11961,7 @@
         <v>0</v>
       </c>
       <c r="I268" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J268" t="n">
         <v>1</v>
@@ -12004,7 +12004,7 @@
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J274" t="n">
         <v>1</v>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -12391,7 +12391,7 @@
         <v>0</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J281" t="n">
         <v>1</v>
@@ -12606,7 +12606,7 @@
         <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -12907,7 +12907,7 @@
         <v>0</v>
       </c>
       <c r="I290" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -12950,7 +12950,7 @@
         <v>0</v>
       </c>
       <c r="I291" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J291" t="n">
         <v>1</v>
@@ -13165,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="I296" t="n">
-        <v>0.666667</v>
+        <v>0.6</v>
       </c>
       <c r="J296" t="n">
         <v>1</v>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="I299" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J299" t="n">
         <v>1</v>
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J300" t="n">
         <v>1</v>
@@ -13423,7 +13423,7 @@
         <v>0</v>
       </c>
       <c r="I302" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J302" t="n">
         <v>1</v>
@@ -13466,7 +13466,7 @@
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J303" t="n">
         <v>1</v>
@@ -13509,7 +13509,7 @@
         <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J304" t="n">
         <v>1</v>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J306" t="n">
         <v>1</v>
@@ -13638,7 +13638,7 @@
         <v>0</v>
       </c>
       <c r="I307" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J307" t="n">
         <v>1</v>
@@ -13681,7 +13681,7 @@
         <v>1</v>
       </c>
       <c r="I308" t="n">
-        <v>0.666667</v>
+        <v>0.6</v>
       </c>
       <c r="J308" t="n">
         <v>1</v>
@@ -13724,7 +13724,7 @@
         <v>1</v>
       </c>
       <c r="I309" t="n">
-        <v>0.666667</v>
+        <v>0.6</v>
       </c>
       <c r="J309" t="n">
         <v>1</v>
@@ -13853,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="I312" t="n">
-        <v>0.333333</v>
+        <v>0.2</v>
       </c>
       <c r="J312" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>0.818006</v>
+        <v>0.907566</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.124109</v>
+        <v>0.144902</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.368825</v>
+        <v>0.196918</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.938141</v>
+        <v>0.957488</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.412476</v>
+        <v>0.27828</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.651254</v>
+        <v>0.545314</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.09840699999999999</v>
+        <v>0.14264</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.23376</v>
+        <v>0.130284</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.386833</v>
+        <v>0.312571</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.251103</v>
+        <v>0.152876</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.359001</v>
+        <v>0.297733</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.270035</v>
+        <v>0.212465</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0.678471</v>
+        <v>0.509703</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.322368</v>
+        <v>0.277369</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.474878</v>
+        <v>0.481965</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.338946</v>
+        <v>0.275541</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.394861</v>
+        <v>0.346534</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>0.463231</v>
+        <v>0.465195</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.451106</v>
+        <v>0.422905</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.258469</v>
+        <v>0.226265</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.410781</v>
+        <v>0.269</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.412232</v>
+        <v>0.324452</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.265715</v>
+        <v>0.180739</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.466141</v>
+        <v>0.301021</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.753454</v>
+        <v>0.786411</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.800279</v>
+        <v>0.8402230000000001</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.244768</v>
+        <v>0.190613</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0.624916</v>
+        <v>0.649278</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.319161</v>
+        <v>0.29899</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.434624</v>
+        <v>0.427402</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.164205</v>
+        <v>0.139089</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.365449</v>
+        <v>0.373762</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.410365</v>
+        <v>0.346964</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.26739</v>
+        <v>0.206069</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.372113</v>
+        <v>0.310574</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.290101</v>
+        <v>0.243736</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6491,10 +6491,10 @@
         <v>0.001231</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.544697</v>
+        <v>0.476397</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.351517</v>
+        <v>0.232563</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.30758</v>
+        <v>0.229232</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.320552</v>
+        <v>0.218795</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.232456</v>
+        <v>0.260251</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0.891427</v>
+        <v>0.847745</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6749,10 +6749,10 @@
         <v>0.003605</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.538094</v>
+        <v>0.390702</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.182505</v>
+        <v>0.170003</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.273379</v>
+        <v>0.218116</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.147337</v>
+        <v>0.130795</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.713064</v>
+        <v>0.695234</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.976438</v>
+        <v>0.995557</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.20407</v>
+        <v>0.129466</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9350619999999999</v>
+        <v>0.94596</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0.730299</v>
+        <v>0.627275</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7136,10 +7136,10 @@
         <v>3.2e-05</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.573427</v>
+        <v>0.416627</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.476253</v>
+        <v>0.426937</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7222,10 +7222,10 @@
         <v>0.002312</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.517259</v>
+        <v>0.32182</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.450932</v>
+        <v>0.3001</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.279785</v>
+        <v>0.187942</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.303319</v>
+        <v>0.224299</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.301538</v>
+        <v>0.179695</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.883881</v>
+        <v>0.839639</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.31787</v>
+        <v>0.206086</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.30412</v>
+        <v>0.18021</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7566,10 +7566,10 @@
         <v>0.001811</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.5244220000000001</v>
+        <v>0.391643</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.365615</v>
+        <v>0.241981</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7652,10 +7652,10 @@
         <v>0.001749</v>
       </c>
       <c r="F168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0.545336</v>
+        <v>0.438856</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.263594</v>
+        <v>0.18387</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.275017</v>
+        <v>0.119178</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.413692</v>
+        <v>0.189667</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.487484</v>
+        <v>0.429425</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.212587</v>
+        <v>0.148988</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.250689</v>
+        <v>0.25694</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.189747</v>
+        <v>0.156139</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7996,10 +7996,10 @@
         <v>2e-06</v>
       </c>
       <c r="F176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.664405</v>
+        <v>0.467716</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.149022</v>
+        <v>0.192858</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.206272</v>
+        <v>0.185321</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.169488</v>
+        <v>0.116066</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.093753</v>
+        <v>0.089342</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>0.77439</v>
+        <v>0.629601</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.388631</v>
+        <v>0.235777</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.176109</v>
+        <v>0.096729</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.331594</v>
+        <v>0.171353</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.224966</v>
+        <v>0.181842</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.282832</v>
+        <v>0.135244</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="G187" t="n">
-        <v>0.666184</v>
+        <v>0.597287</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.226399</v>
+        <v>0.162183</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.182343</v>
+        <v>0.205947</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.873715</v>
+        <v>0.847986</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.487431</v>
+        <v>0.264453</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>0.809967</v>
+        <v>0.83978</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.390762</v>
+        <v>0.253171</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.400603</v>
+        <v>0.177033</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.388564</v>
+        <v>0.304408</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="G196" t="n">
-        <v>0.865568</v>
+        <v>0.869297</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.922993</v>
+        <v>0.933968</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.867345</v>
+        <v>0.956264</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8985,10 +8985,10 @@
         <v>0.001123</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>0.748059</v>
+        <v>0.426857</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.396071</v>
+        <v>0.451708</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>1</v>
       </c>
       <c r="G201" t="n">
-        <v>0.878634</v>
+        <v>0.763718</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.149256</v>
+        <v>0.042105</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9157,10 +9157,10 @@
         <v>0.001364</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.537192</v>
+        <v>0.27467</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.432227</v>
+        <v>0.261565</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.113012</v>
+        <v>0.021524</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.874973</v>
+        <v>0.966011</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0.562141</v>
+        <v>0.591401</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.300062</v>
+        <v>0.06512999999999999</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9415,10 +9415,10 @@
         <v>0.000295</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.52755</v>
+        <v>0.286542</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.768906</v>
+        <v>0.746389</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.164586</v>
+        <v>0.055046</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.345427</v>
+        <v>0.135075</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.40433</v>
+        <v>0.144409</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.263351</v>
+        <v>0.106184</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.220946</v>
+        <v>0.066952</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0.000373</v>
       </c>
       <c r="F216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.52149</v>
+        <v>0.336909</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.135075</v>
+        <v>0.080621</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0.005524</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.6388740000000001</v>
+        <v>0.413943</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9845,10 +9845,10 @@
         <v>0.008429000000000001</v>
       </c>
       <c r="F219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.517614</v>
+        <v>0.205985</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.184207</v>
+        <v>0.053245</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.355119</v>
+        <v>0.153591</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9974,10 +9974,10 @@
         <v>0.008602</v>
       </c>
       <c r="F222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>0.552893</v>
+        <v>0.407618</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.479403</v>
+        <v>0.450258</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.313835</v>
+        <v>0.187816</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10103,10 +10103,10 @@
         <v>0.006232</v>
       </c>
       <c r="F225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.501261</v>
+        <v>0.299705</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10146,10 +10146,10 @@
         <v>0.029317</v>
       </c>
       <c r="F226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.561329</v>
+        <v>0.458465</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.45439</v>
+        <v>0.32182</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.354764</v>
+        <v>0.120441</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.212277</v>
+        <v>0.088213</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.08619</v>
+        <v>0.033659</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.52964</v>
+        <v>0.868345</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.221555</v>
+        <v>0.115166</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0.321092</v>
+        <v>0.412453</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10490,10 +10490,10 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0.285001</v>
+        <v>0.515309</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.9302820000000001</v>
+        <v>0.996101</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.30652</v>
+        <v>0.107563</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.209498</v>
+        <v>0.026475</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.20758</v>
+        <v>0.055965</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.214805</v>
+        <v>0.059268</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.184975</v>
+        <v>0.052808</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.222647</v>
+        <v>0.057894</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.127914</v>
+        <v>0.02208</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0.001803</v>
       </c>
       <c r="F243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.627205</v>
+        <v>0.384739</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="G244" t="n">
-        <v>0.796082</v>
+        <v>0.582666</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10963,10 +10963,10 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0.513355</v>
+        <v>0.351185</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.799498</v>
+        <v>0.96482</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.898407</v>
+        <v>0.981393</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.752736</v>
+        <v>0.8925149999999999</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.875406</v>
+        <v>0.979532</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>1</v>
       </c>
       <c r="G250" t="n">
-        <v>0.63518</v>
+        <v>0.560994</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.286048</v>
+        <v>0.160627</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11264,10 +11264,10 @@
         <v>0.067122</v>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>0.509416</v>
+        <v>0.107976</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.097501</v>
+        <v>0.014921</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.373066</v>
+        <v>0.387512</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.429051</v>
+        <v>0.413404</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.654989</v>
+        <v>0.593333</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.933084</v>
+        <v>0.986322</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.93189</v>
+        <v>0.995227</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>0.459176</v>
+        <v>0.197607</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.16589</v>
+        <v>0.061009</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.911269</v>
+        <v>0.932563</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.482898</v>
+        <v>0.229346</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.336063</v>
+        <v>0.27006</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.990796</v>
+        <v>0.9998280000000001</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11823,10 +11823,10 @@
         <v>0</v>
       </c>
       <c r="F265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.564098</v>
+        <v>0.438948</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.077089</v>
+        <v>0.014602</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.80171</v>
+        <v>0.808653</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.9452739999999999</v>
+        <v>0.975276</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.35084</v>
+        <v>0.244727</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.256986</v>
+        <v>0.08314100000000001</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.131504</v>
+        <v>0.03939</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>0.5504829999999999</v>
+        <v>0.594787</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12167,10 +12167,10 @@
         <v>0.000144</v>
       </c>
       <c r="F273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0.6515069999999999</v>
+        <v>0.442966</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.702508</v>
+        <v>0.670479</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.382551</v>
+        <v>0.099014</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>0.358668</v>
+        <v>0.091987</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12339,10 +12339,10 @@
         <v>0.000104</v>
       </c>
       <c r="F277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.505453</v>
+        <v>0.280596</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.464143</v>
+        <v>0.169855</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.209675</v>
+        <v>0.061566</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.171464</v>
+        <v>0.071482</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.271333</v>
+        <v>0.121946</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.217319</v>
+        <v>0.09224499999999999</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.354721</v>
+        <v>0.145041</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.331169</v>
+        <v>0.133758</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.277398</v>
+        <v>0.068242</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.331426</v>
+        <v>0.14963</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.853063</v>
+        <v>0.980826</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>0.61536</v>
+        <v>0.721504</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.452765</v>
+        <v>0.203788</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.224935</v>
+        <v>0.076488</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>0.90722</v>
+        <v>0.6939109999999999</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.368181</v>
+        <v>0.09562</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13027,10 +13027,10 @@
         <v>7e-06</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.547905</v>
+        <v>0.209117</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.205577</v>
+        <v>0.055071</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.251125</v>
+        <v>0.088309</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.997578</v>
+        <v>1</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0.6640160000000001</v>
+        <v>0.609912</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.489852</v>
+        <v>0.420656</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>1</v>
       </c>
       <c r="G299" t="n">
-        <v>0.63656</v>
+        <v>0.632834</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0.719534</v>
+        <v>0.684622</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.173185</v>
+        <v>0.086339</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.234086</v>
+        <v>0.060751</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.952231</v>
+        <v>0.995478</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.922909</v>
+        <v>0.978831</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.195758</v>
+        <v>0.06310300000000001</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13586,10 +13586,10 @@
         <v>0.000783</v>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.51202</v>
+        <v>0.382525</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.41321</v>
+        <v>0.339319</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>0.795548</v>
+        <v>0.78346</v>
       </c>
       <c r="H308" t="n">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.891353</v>
+        <v>0.840546</v>
       </c>
       <c r="H309" t="n">
         <v>1</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.198566</v>
+        <v>0.072106</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.329293</v>
+        <v>0.121524</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.093443</v>
+        <v>0.016487</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.272064</v>
+        <v>0.182323</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
